--- a/data/Tuning/FISC inyear extract QMFM SI Oct17 adjAK Oct25.xlsx
+++ b/data/Tuning/FISC inyear extract QMFM SI Oct17 adjAK Oct25.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AKDocs\aa Local Docs\MyWorkingDocs\AK files\Rwa\MU-MF\MUiMF\integratedMF\2025\r FISCAL March April 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\MINECOFIN\Macro\Modeling\QMFM\data\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E231623F-4E5C-43EA-B85B-3638CD183E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA17AE1F-58C1-4F92-BD26-9838B0450877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" firstSheet="1" activeTab="1" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
   </bookViews>
   <sheets>
     <sheet name="FiscTuning_Rw" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="NKIA Financing" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="fiscal_tunes">FiscTuning_Rw!$A$36:$AT$78</definedName>
@@ -23,17 +23,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -101,8 +90,43 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{70BEE8D7-393D-40E0-9E7F-9C769B398578}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+From Bugesera tables  september
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="78">
   <si>
     <t>Extract from FISCAL in-year, with corrected GDP numbers, lonked to intMF FY GDP</t>
   </si>
@@ -371,12 +395,30 @@
   <si>
     <t xml:space="preserve">    O/w Bugesera </t>
   </si>
+  <si>
+    <t xml:space="preserve">        Adjust big project (Bugesera) in mln USD (DFI + Equity+ Ext.loans, also in BOP; ATL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bugesera Qatar FDI Equity (from 2025 as in BOP in mln USD) </t>
+  </si>
+  <si>
+    <t>Bugesera Govt Equity (ATL) (from 2024 as in BOP in mln USD)</t>
+  </si>
+  <si>
+    <t>Exchange rate RWF/USD (end of period) CY</t>
+  </si>
+  <si>
+    <t>Depr rate</t>
+  </si>
+  <si>
+    <t>FY</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
@@ -384,8 +426,9 @@
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,8 +696,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -691,8 +768,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -931,6 +1020,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -938,7 +1054,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1079,6 +1195,21 @@
     <xf numFmtId="9" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="167" fontId="40" fillId="8" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="37" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="37" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1420,7 +1551,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:BC79"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" outlineLevelCol="1" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="43.26953125" customWidth="1"/>
     <col min="2" max="25" width="8.7265625" hidden="1" customWidth="1" outlineLevel="1"/>
@@ -1432,12 +1563,12 @@
     <col min="53" max="53" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" s="8" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" s="8" customFormat="1" ht="11.5" x14ac:dyDescent="0.5">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
@@ -1591,7 +1722,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A6" s="9" t="s">
         <v>19</v>
       </c>
@@ -1749,7 +1880,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A7" s="13" t="s">
         <v>26</v>
       </c>
@@ -1837,7 +1968,7 @@
         <v>36327.523609205775</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -1925,7 +2056,7 @@
         <v>0.20661377678750092</v>
       </c>
     </row>
-    <row r="9" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A9" s="13" t="s">
         <v>28</v>
       </c>
@@ -2013,7 +2144,7 @@
         <v>0.21652717851044984</v>
       </c>
     </row>
-    <row r="10" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A10" s="13" t="s">
         <v>29</v>
       </c>
@@ -2101,7 +2232,7 @@
         <v>4.6238458036064918E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A11" s="13"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -2155,7 +2286,7 @@
       <c r="AY11" s="15"/>
       <c r="AZ11" s="15"/>
     </row>
-    <row r="12" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A12" s="13"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -2209,7 +2340,7 @@
       <c r="AY12" s="15"/>
       <c r="AZ12" s="15"/>
     </row>
-    <row r="13" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A13" s="13" t="s">
         <v>30</v>
       </c>
@@ -2297,7 +2428,7 @@
         <v>0.2627656365465148</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A14" s="13" t="s">
         <v>31</v>
       </c>
@@ -2385,7 +2516,7 @@
         <v>-5.6151859759013864E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A15" s="13"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -2439,7 +2570,7 @@
       <c r="AY15" s="12"/>
       <c r="AZ15" s="12"/>
     </row>
-    <row r="16" spans="1:52" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:52" ht="13.5" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="9" t="s">
         <v>32</v>
       </c>
@@ -2495,7 +2626,7 @@
       <c r="AY16" s="22"/>
       <c r="AZ16" s="22"/>
     </row>
-    <row r="17" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A17" s="13" t="s">
         <v>33</v>
       </c>
@@ -2653,7 +2784,7 @@
         <v>7539.082760930628</v>
       </c>
     </row>
-    <row r="18" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A18" s="13" t="s">
         <v>34</v>
       </c>
@@ -2811,7 +2942,7 @@
         <v>8271.8277447682412</v>
       </c>
     </row>
-    <row r="19" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A19" s="13" t="s">
         <v>35</v>
       </c>
@@ -2969,7 +3100,7 @@
         <v>1255.8638445821318</v>
       </c>
     </row>
-    <row r="20" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A20" s="13" t="s">
         <v>70</v>
       </c>
@@ -3079,7 +3210,7 @@
         <v>65.783991693740418</v>
       </c>
     </row>
-    <row r="21" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A21" s="13" t="s">
         <v>71</v>
       </c>
@@ -3189,7 +3320,7 @@
         <v>36.892497357740417</v>
       </c>
     </row>
-    <row r="22" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A22" s="13" t="s">
         <v>36</v>
       </c>
@@ -3347,7 +3478,7 @@
         <v>9527.6915893503738</v>
       </c>
     </row>
-    <row r="23" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A23" s="13" t="s">
         <v>37</v>
       </c>
@@ -3505,7 +3636,7 @@
         <v>-1988.6088284197472</v>
       </c>
     </row>
-    <row r="24" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A24" s="26" t="s">
         <v>38</v>
       </c>
@@ -3663,7 +3794,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A25" s="28"/>
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
@@ -3731,7 +3862,7 @@
       <c r="AY25" s="31"/>
       <c r="AZ25" s="31"/>
     </row>
-    <row r="26" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A26" s="13"/>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
@@ -3831,7 +3962,7 @@
       <c r="AY26" s="25"/>
       <c r="AZ26" s="25"/>
     </row>
-    <row r="27" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A27" s="13" t="s">
         <v>26</v>
       </c>
@@ -3989,7 +4120,7 @@
         <v>39154.682745506419</v>
       </c>
     </row>
-    <row r="28" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A28" s="13" t="s">
         <v>27</v>
       </c>
@@ -4147,7 +4278,7 @@
         <v>0.19254613324113448</v>
       </c>
     </row>
-    <row r="29" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A29" s="13" t="s">
         <v>28</v>
       </c>
@@ -4305,7 +4436,7 @@
         <v>0.21126024180894573</v>
       </c>
     </row>
-    <row r="30" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A30" s="13" t="s">
         <v>29</v>
       </c>
@@ -4463,7 +4594,7 @@
         <v>3.2074422687699104E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A31" s="13" t="s">
         <v>70</v>
       </c>
@@ -4573,7 +4704,7 @@
         <v>1.6801053432437812E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A32" s="13" t="s">
         <v>71</v>
       </c>
@@ -4683,7 +4814,7 @@
         <v>9.4222439746301809E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A33" s="13" t="s">
         <v>30</v>
       </c>
@@ -4841,7 +4972,7 @@
         <v>0.24333466449664484</v>
       </c>
     </row>
-    <row r="34" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A34" s="13" t="s">
         <v>31</v>
       </c>
@@ -4999,12 +5130,12 @@
         <v>-5.0788531255510416E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A35" s="40" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A36" s="41" t="s">
         <v>41</v>
       </c>
@@ -5075,7 +5206,7 @@
         <v>2029/2030</v>
       </c>
     </row>
-    <row r="37" spans="1:52" ht="16" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A37" s="46" t="str">
         <f>+A34</f>
         <v>Deficit (Excl. Grants ) % of GDP</v>
@@ -5153,7 +5284,7 @@
         <v>-5.0788531255510416E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A38" s="99" t="str">
         <f>+A51</f>
         <v xml:space="preserve">correction </v>
@@ -5219,7 +5350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:52" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A39" s="49" t="s">
         <v>42</v>
       </c>
@@ -5284,7 +5415,7 @@
         <v>-5.0788531255510416E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:52" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -5331,7 +5462,7 @@
         <v>-5.0430582505264485E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:52" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -5396,8 +5527,8 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:52" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:52" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75"/>
+    <row r="43" spans="1:52" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A43" s="65" t="str">
         <f>+A28</f>
         <v>Grev in % of GDP</v>
@@ -5475,7 +5606,7 @@
         <v>0.19254613324113448</v>
       </c>
     </row>
-    <row r="44" spans="1:52" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:52" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A44" s="99" t="str">
         <f>+A51</f>
         <v xml:space="preserve">correction </v>
@@ -5539,7 +5670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:52" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:52" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A45" s="49" t="s">
         <v>66</v>
       </c>
@@ -5610,7 +5741,7 @@
         <v>0.19254613324113448</v>
       </c>
     </row>
-    <row r="46" spans="1:52" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -5668,7 +5799,7 @@
       </c>
       <c r="AZ46" s="15"/>
     </row>
-    <row r="47" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:52" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -5745,7 +5876,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:52" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="AI48" s="66">
         <v>2E-3</v>
       </c>
@@ -5807,7 +5938,7 @@
         <v>0.19315000000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:55" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:55" x14ac:dyDescent="0.75">
       <c r="AI49" s="66"/>
       <c r="AJ49" s="66"/>
       <c r="AK49" s="66"/>
@@ -5827,7 +5958,7 @@
       <c r="AY49" s="66"/>
       <c r="AZ49" s="66"/>
     </row>
-    <row r="50" spans="1:55" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:55" ht="15.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A50" s="65" t="str">
         <f>+A29</f>
         <v>Gdem in % of GDP</v>
@@ -5905,7 +6036,7 @@
         <v>0.21126024180894573</v>
       </c>
     </row>
-    <row r="51" spans="1:55" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:55" x14ac:dyDescent="0.75">
       <c r="A51" s="67" t="s">
         <v>47</v>
       </c>
@@ -5976,7 +6107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A52" s="49" t="s">
         <v>67</v>
       </c>
@@ -6053,7 +6184,7 @@
         <v>0.21126024180894573</v>
       </c>
     </row>
-    <row r="53" spans="1:55" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:55" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -6106,7 +6237,7 @@
       </c>
       <c r="AZ53" s="57"/>
     </row>
-    <row r="54" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A54" t="str">
         <f>+A47</f>
         <v xml:space="preserve">                                                 second Q in sem</v>
@@ -6175,7 +6306,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:55" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:55" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="AI55" s="15"/>
       <c r="AJ55" s="15"/>
       <c r="AK55" s="15"/>
@@ -6195,7 +6326,7 @@
       <c r="AY55" s="15"/>
       <c r="AZ55" s="15"/>
     </row>
-    <row r="56" spans="1:55" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:55" x14ac:dyDescent="0.75">
       <c r="A56" s="65" t="str">
         <f>+A30</f>
         <v>Other Expenditure of %GDP</v>
@@ -6273,7 +6404,7 @@
         <v>3.2074422687699104E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:55" s="70" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:55" s="70" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A57" s="70" t="s">
         <v>49</v>
       </c>
@@ -6350,7 +6481,7 @@
         <v>9.4222439746301809E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:55" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:55" s="67" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A58" s="67" t="str">
         <f>+A38</f>
         <v xml:space="preserve">correction </v>
@@ -6426,7 +6557,7 @@
       <c r="BB58" s="68"/>
       <c r="BC58" s="68"/>
     </row>
-    <row r="59" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A59" s="49" t="s">
         <v>50</v>
       </c>
@@ -6506,7 +6637,7 @@
       <c r="BB59" s="50"/>
       <c r="BC59" s="50"/>
     </row>
-    <row r="60" spans="1:55" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:55" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>51</v>
       </c>
@@ -6556,7 +6687,7 @@
       </c>
       <c r="AZ60" s="57"/>
     </row>
-    <row r="61" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A61" t="str">
         <f>+A54</f>
         <v xml:space="preserve">                                                 second Q in sem</v>
@@ -6622,7 +6753,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:55" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:55" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -6647,7 +6778,7 @@
         <v>3.1132198290236085E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A64" s="76" t="s">
         <v>52</v>
       </c>
@@ -6724,7 +6855,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:53" x14ac:dyDescent="0.75">
       <c r="A65" s="76" t="str">
         <f>+A64</f>
         <v>check</v>
@@ -6805,7 +6936,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:53" x14ac:dyDescent="0.75">
       <c r="AI66" s="94" t="s">
         <v>52</v>
       </c>
@@ -6813,7 +6944,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:53" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>61</v>
       </c>
@@ -6891,7 +7022,7 @@
         <v>1508.1120582726448</v>
       </c>
     </row>
-    <row r="68" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:53" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>62</v>
       </c>
@@ -6916,7 +7047,7 @@
       <c r="AY68" s="82"/>
       <c r="AZ68" s="82"/>
     </row>
-    <row r="69" spans="1:53" s="70" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:53" s="70" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A69" s="70" t="s">
         <v>53</v>
       </c>
@@ -6990,7 +7121,7 @@
         <v>9.4222439746301809E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:53" x14ac:dyDescent="0.75">
       <c r="AL71" s="44" t="str">
         <f>+AL36</f>
         <v>Jul-Dec</v>
@@ -7017,12 +7148,12 @@
       </c>
       <c r="AR71" s="44"/>
     </row>
-    <row r="72" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:53" x14ac:dyDescent="0.75">
       <c r="AJ72" s="92" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:53" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A73" s="65" t="s">
         <v>68</v>
       </c>
@@ -7072,7 +7203,7 @@
       <c r="AY73" s="47"/>
       <c r="AZ73" s="47"/>
     </row>
-    <row r="74" spans="1:53" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:53" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="A74" s="70" t="s">
         <v>54</v>
       </c>
@@ -7107,7 +7238,7 @@
       </c>
       <c r="AT74" s="55"/>
     </row>
-    <row r="75" spans="1:53" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:53" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A75" s="70" t="s">
         <v>56</v>
       </c>
@@ -7151,12 +7282,12 @@
         <v>4.124610152328733E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:53" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:53" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="A76" s="70"/>
       <c r="AJ76" s="89"/>
       <c r="AN76" s="105"/>
     </row>
-    <row r="77" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:53" x14ac:dyDescent="0.75">
       <c r="AJ77" s="45" t="s">
         <v>58</v>
       </c>
@@ -7184,7 +7315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:53" x14ac:dyDescent="0.75">
       <c r="AJ78" s="90">
         <v>0.5</v>
       </c>
@@ -7209,7 +7340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:53" x14ac:dyDescent="0.75">
       <c r="A79" s="91" t="s">
         <v>59</v>
       </c>
@@ -7223,23 +7354,214 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD3143F-1CB5-4284-805F-149289AA16B5}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD3143F-1CB5-4284-805F-149289AA16B5}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="53.6796875" customWidth="1"/>
+    <col min="2" max="8" width="8.86328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A1" s="1"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B1" s="114">
+        <v>2024</v>
+      </c>
+      <c r="C1" s="114">
+        <v>2025</v>
+      </c>
+      <c r="D1" s="114">
+        <v>2026</v>
+      </c>
+      <c r="E1" s="114">
+        <v>2027</v>
+      </c>
+      <c r="F1" s="114">
+        <v>2028</v>
+      </c>
+      <c r="G1" s="114">
+        <v>2029</v>
+      </c>
+      <c r="H1" s="114">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A2" s="106" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="110">
+        <f>C3+C4</f>
+        <v>308.85861037162039</v>
+      </c>
+      <c r="D2" s="110">
+        <f t="shared" ref="D2:G2" si="0">D3+D4</f>
+        <v>721.33994120659054</v>
+      </c>
+      <c r="E2" s="110">
+        <f t="shared" si="0"/>
+        <v>732.21927019834698</v>
+      </c>
+      <c r="F2" s="110">
+        <f t="shared" si="0"/>
+        <v>187.93653864476565</v>
+      </c>
+      <c r="G2" s="110">
+        <f t="shared" si="0"/>
+        <v>4.2285111869296426</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A3" s="107" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="110">
+        <v>174.00361037162037</v>
+      </c>
+      <c r="D3" s="110">
+        <v>385.4857976103541</v>
+      </c>
+      <c r="E3" s="110">
+        <v>439.33156211900854</v>
+      </c>
+      <c r="F3" s="110">
+        <v>112.76192318685943</v>
+      </c>
+      <c r="G3" s="110">
+        <v>2.5371067121577857</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A4" s="107" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="111">
+        <v>134.85500000000002</v>
+      </c>
+      <c r="D4" s="111">
+        <v>335.85414359623644</v>
+      </c>
+      <c r="E4" s="111">
+        <v>292.88770807933849</v>
+      </c>
+      <c r="F4" s="111">
+        <v>75.174615457906214</v>
+      </c>
+      <c r="G4" s="111">
+        <v>1.6914044747718571</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A6" s="108" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="109">
+        <v>1382.9873419999999</v>
+      </c>
+      <c r="C6" s="109">
+        <v>1455.0205468858974</v>
+      </c>
+      <c r="D6" s="109">
+        <v>1517.7698205635791</v>
+      </c>
+      <c r="E6" s="109">
+        <v>1572.0012687572651</v>
+      </c>
+      <c r="F6" s="109">
+        <v>1615.7148947336634</v>
+      </c>
+      <c r="G6" s="109">
+        <v>1656.1077671020048</v>
+      </c>
+      <c r="H6" s="109">
+        <v>1697.5104612795549</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="112">
+        <f>C6/B6-1</f>
+        <v>5.2085223557958971E-2</v>
+      </c>
+      <c r="D7" s="112">
+        <f t="shared" ref="D7:H7" si="1">D6/C6-1</f>
+        <v>4.312603956829375E-2</v>
+      </c>
+      <c r="E7" s="112">
+        <f t="shared" si="1"/>
+        <v>3.5731009708408035E-2</v>
+      </c>
+      <c r="F7" s="112">
+        <f t="shared" si="1"/>
+        <v>2.7807627668746004E-2</v>
+      </c>
+      <c r="G7" s="112">
+        <f t="shared" si="1"/>
+        <v>2.4999999999999911E-2</v>
+      </c>
+      <c r="H7" s="112">
+        <f t="shared" si="1"/>
+        <v>2.4999999999999911E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="109">
+        <v>1256.9432939166666</v>
+      </c>
+      <c r="C8" s="109">
+        <v>1370.8647181798078</v>
+      </c>
+      <c r="D8" s="109">
+        <v>1452.6995640838434</v>
+      </c>
+      <c r="E8" s="109">
+        <v>1515.6403641925801</v>
+      </c>
+      <c r="F8" s="109">
+        <v>1569.371813202943</v>
+      </c>
+      <c r="G8" s="109">
+        <v>1614.8847063316493</v>
+      </c>
+      <c r="H8" s="109">
+        <v>1656.360222554307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="C9" s="112"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="C10" s="113">
+        <f>C2*C6/1000</f>
+        <v>449.39562417333343</v>
+      </c>
+      <c r="D10" s="113">
+        <f t="shared" ref="D10:G10" si="2">D2*D6/1000</f>
+        <v>1094.8279931304696</v>
+      </c>
+      <c r="E10" s="113">
+        <f t="shared" si="2"/>
+        <v>1151.0496217603202</v>
+      </c>
+      <c r="F10" s="113">
+        <f t="shared" si="2"/>
+        <v>303.65186475303659</v>
+      </c>
+      <c r="G10" s="113">
+        <f t="shared" si="2"/>
+        <v>7.0028702199518982</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Tuning/FISC inyear extract QMFM SI Oct17 adjAK Oct25.xlsx
+++ b/data/Tuning/FISC inyear extract QMFM SI Oct17 adjAK Oct25.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\MINECOFIN\Macro\Modeling\QMFM\data\2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swadiq.ishimwe\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\RJK8FGLW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA17AE1F-58C1-4F92-BD26-9838B0450877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6AEAFAE-10DA-4945-BE74-4EB6D1DD23C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" firstSheet="1" activeTab="1" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
   </bookViews>
   <sheets>
     <sheet name="FiscTuning_Rw" sheetId="2" r:id="rId1"/>
-    <sheet name="NKIA Financing" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="fiscal_tunes">FiscTuning_Rw!$A$36:$AT$78</definedName>
@@ -23,6 +23,18 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -90,43 +102,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{70BEE8D7-393D-40E0-9E7F-9C769B398578}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-From Bugesera tables  september
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
   <si>
     <t>Extract from FISCAL in-year, with corrected GDP numbers, lonked to intMF FY GDP</t>
   </si>
@@ -183,9 +160,6 @@
   </si>
   <si>
     <t>2029/2030</t>
-  </si>
-  <si>
-    <t>March 2025 Revision</t>
   </si>
   <si>
     <t>Jul-Dec</t>
@@ -320,9 +294,6 @@
     <t>2025-29</t>
   </si>
   <si>
-    <t>sum 25-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">     PM oexp excl. Bugesera</t>
   </si>
   <si>
@@ -396,39 +367,26 @@
     <t xml:space="preserve">    O/w Bugesera </t>
   </si>
   <si>
-    <t xml:space="preserve">        Adjust big project (Bugesera) in mln USD (DFI + Equity+ Ext.loans, also in BOP; ATL)</t>
+    <t xml:space="preserve">            O/w Bugesera </t>
   </si>
   <si>
-    <t xml:space="preserve">Bugesera Qatar FDI Equity (from 2025 as in BOP in mln USD) </t>
-  </si>
-  <si>
-    <t>Bugesera Govt Equity (ATL) (from 2024 as in BOP in mln USD)</t>
-  </si>
-  <si>
-    <t>Exchange rate RWF/USD (end of period) CY</t>
-  </si>
-  <si>
-    <t>Depr rate</t>
-  </si>
-  <si>
-    <t>FY</t>
+    <t>March 2026 Revision</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,42 +654,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -768,20 +692,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="25">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1020,147 +932,120 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="14" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="13" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="13" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="12" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="13" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1169,13 +1054,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="29" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="30" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="23" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="29" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="30" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="23" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="23" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="23" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1189,27 +1074,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="8" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="37" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="37" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1551,24 +1421,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:BC79"/>
-  <sheetFormatPr defaultRowHeight="14.75" outlineLevelCol="1" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="13.8" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="43.26953125" customWidth="1"/>
-    <col min="2" max="25" width="8.7265625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="10.6328125" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="30" width="10.6328125" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="11.81640625" hidden="1" customWidth="1"/>
-    <col min="32" max="34" width="8.6328125" style="3" hidden="1" customWidth="1"/>
-    <col min="35" max="52" width="9.6328125" style="3" customWidth="1"/>
-    <col min="53" max="53" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.28515625" customWidth="1"/>
+    <col min="2" max="25" width="8.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="10.6171875" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="27" max="30" width="10.6171875" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="11.80859375" hidden="1" customWidth="1"/>
+    <col min="32" max="34" width="8.6171875" style="3" hidden="1" customWidth="1"/>
+    <col min="35" max="52" width="9.6171875" style="3" customWidth="1"/>
+    <col min="53" max="53" width="9.1875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" s="8" customFormat="1" ht="11.5" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:52" s="8" customFormat="1" ht="11.1">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
@@ -1722,167 +1592,167 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="6" spans="1:52" ht="15">
       <c r="A6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="C6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="H6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="M6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="10" t="s">
+      <c r="N6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="R6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AK6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AQ6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AS6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AT6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AV6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AZ6" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" ht="15.3">
+      <c r="A7" s="13" t="s">
         <v>25</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="R6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="S6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="T6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="V6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="W6" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="X6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z6" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC6" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AJ6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AL6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AM6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AO6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AR6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AS6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AT6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AU6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AX6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AY6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ6" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:52" ht="16" x14ac:dyDescent="0.8">
-      <c r="A7" s="13" t="s">
-        <v>26</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -1920,57 +1790,57 @@
       <c r="AI7" s="14"/>
       <c r="AJ7" s="14"/>
       <c r="AK7" s="14">
-        <v>20033.689823079447</v>
+        <v>21512</v>
       </c>
       <c r="AL7" s="14">
-        <v>11326.738119159327</v>
+        <v>12719.344769322401</v>
       </c>
       <c r="AM7" s="14">
-        <v>11326.738119159327</v>
+        <v>12719.344769322401</v>
       </c>
       <c r="AN7" s="14">
-        <v>22653.476238318653</v>
+        <v>25438.689538644801</v>
       </c>
       <c r="AO7" s="14">
-        <v>12781.239907852294</v>
+        <v>14684.878547616787</v>
       </c>
       <c r="AP7" s="14">
-        <v>12781.239907852294</v>
+        <v>14684.878547616787</v>
       </c>
       <c r="AQ7" s="14">
-        <v>25562.479815704588</v>
+        <v>29369.757095233574</v>
       </c>
       <c r="AR7" s="14">
-        <v>14387.536018309578</v>
+        <v>16584.620036406115</v>
       </c>
       <c r="AS7" s="14">
-        <v>14387.536018309578</v>
+        <v>16584.620036406115</v>
       </c>
       <c r="AT7" s="14">
-        <v>28775.072036619156</v>
+        <v>33169.24007281223</v>
       </c>
       <c r="AU7" s="14">
-        <v>16166.704197489691</v>
+        <v>18629.018513773546</v>
       </c>
       <c r="AV7" s="14">
-        <v>16166.704197489691</v>
+        <v>18629.018513773546</v>
       </c>
       <c r="AW7" s="14">
-        <v>32333.408394979382</v>
+        <v>37258.037027547092</v>
       </c>
       <c r="AX7" s="14">
-        <v>18163.761804602887</v>
+        <v>20932.087692283047</v>
       </c>
       <c r="AY7" s="14">
-        <v>18163.761804602887</v>
+        <v>20932.087692283047</v>
       </c>
       <c r="AZ7" s="14">
-        <v>36327.523609205775</v>
-      </c>
-    </row>
-    <row r="8" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+        <v>41864.175384566093</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" ht="15.3">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -2008,57 +1878,57 @@
       <c r="AI8" s="15"/>
       <c r="AJ8" s="15"/>
       <c r="AK8" s="15">
-        <v>0.18265969901885684</v>
+        <v>0.16546014323811883</v>
       </c>
       <c r="AL8" s="15">
-        <v>0.18202180406841192</v>
+        <v>0.16307315624292407</v>
       </c>
       <c r="AM8" s="15">
-        <v>0.19342862639163508</v>
+        <v>0.17828931704799833</v>
       </c>
       <c r="AN8" s="15">
-        <v>0.1877252152300235</v>
+        <v>0.1706812366454612</v>
       </c>
       <c r="AO8" s="15">
-        <v>0.19131015743891358</v>
+        <v>0.17061480586591948</v>
       </c>
       <c r="AP8" s="15">
-        <v>0.20347286117005281</v>
+        <v>0.18072531776616066</v>
       </c>
       <c r="AQ8" s="15">
-        <v>0.19739150930448318</v>
+        <v>0.17567006181604009</v>
       </c>
       <c r="AR8" s="15">
-        <v>0.19639922020301412</v>
+        <v>0.17404007093305077</v>
       </c>
       <c r="AS8" s="15">
-        <v>0.20882982480919066</v>
+        <v>0.18486167792584693</v>
       </c>
       <c r="AT8" s="15">
-        <v>0.20261452250610237</v>
+        <v>0.17945087442944885</v>
       </c>
       <c r="AU8" s="15">
-        <v>0.19848358609826458</v>
+        <v>0.17637767996445769</v>
       </c>
       <c r="AV8" s="15">
-        <v>0.21105666189556113</v>
+        <v>0.18731792293447977</v>
       </c>
       <c r="AW8" s="15">
-        <v>0.20477012399691286</v>
+        <v>0.18184780144946874</v>
       </c>
       <c r="AX8" s="15">
-        <v>0.20026130698200914</v>
+        <v>0.17820202086685463</v>
       </c>
       <c r="AY8" s="15">
-        <v>0.21296624659299274</v>
+        <v>0.18922447493438097</v>
       </c>
       <c r="AZ8" s="15">
-        <v>0.20661377678750092</v>
-      </c>
-    </row>
-    <row r="9" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+        <v>0.1837132479006178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:52" ht="15.3">
       <c r="A9" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -2096,57 +1966,57 @@
       <c r="AI9" s="15"/>
       <c r="AJ9" s="15"/>
       <c r="AK9" s="15">
-        <v>0.21618191762249483</v>
+        <v>0.20053719230054018</v>
       </c>
       <c r="AL9" s="15">
-        <v>0.22207929529235795</v>
+        <v>0.18828649942779166</v>
       </c>
       <c r="AM9" s="15">
-        <v>0.18220563884602761</v>
+        <v>0.19110022215069525</v>
       </c>
       <c r="AN9" s="15">
-        <v>0.20214246706919278</v>
+        <v>0.18969336078924348</v>
       </c>
       <c r="AO9" s="15">
-        <v>0.23085905359127892</v>
+        <v>0.18928740330000102</v>
       </c>
       <c r="AP9" s="15">
-        <v>0.19146428712535027</v>
+        <v>0.18040876655958882</v>
       </c>
       <c r="AQ9" s="15">
-        <v>0.2111616703583146</v>
+        <v>0.18484808492979496</v>
       </c>
       <c r="AR9" s="15">
-        <v>0.1708666529724199</v>
+        <v>0.19484990460117188</v>
       </c>
       <c r="AS9" s="15">
-        <v>0.14106344180139738</v>
+        <v>0.18503034888548991</v>
       </c>
       <c r="AT9" s="15">
-        <v>0.21736809529944531</v>
+        <v>0.18994012674333088</v>
       </c>
       <c r="AU9" s="15">
-        <v>0.16912216075845865</v>
+        <v>0.20936618216901065</v>
       </c>
       <c r="AV9" s="15">
-        <v>0.14565705261025019</v>
+        <v>0.17957404570351287</v>
       </c>
       <c r="AW9" s="15">
-        <v>0.21938605929611971</v>
+        <v>0.19447011393626176</v>
       </c>
       <c r="AX9" s="15">
-        <v>0.16615357804585285</v>
+        <v>0.20058474431071402</v>
       </c>
       <c r="AY9" s="15">
-        <v>0.14627159152842076</v>
+        <v>0.19462159095390191</v>
       </c>
       <c r="AZ9" s="15">
-        <v>0.21652717851044984</v>
-      </c>
-    </row>
-    <row r="10" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+        <v>0.19760316763230795</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" ht="15.3">
       <c r="A10" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -2184,55 +2054,55 @@
       <c r="AI10" s="15"/>
       <c r="AJ10" s="15"/>
       <c r="AK10" s="15">
-        <v>5.2313276029538544E-2</v>
+        <v>4.8267929014096267E-2</v>
       </c>
       <c r="AL10" s="15">
-        <v>0.12451984317227541</v>
+        <v>5.5650796566345063E-2</v>
       </c>
       <c r="AM10" s="15">
-        <v>4.5857654055867912E-2</v>
+        <v>7.3326752659246916E-2</v>
       </c>
       <c r="AN10" s="15">
-        <v>8.5188748614071663E-2</v>
+        <v>6.4386587928884811E-2</v>
       </c>
       <c r="AO10" s="15">
-        <v>7.4739109667772821E-2</v>
+        <v>5.7724847737669852E-2</v>
       </c>
       <c r="AP10" s="15">
-        <v>5.8352899484848814E-2</v>
+        <v>5.7322632183083554E-2</v>
       </c>
       <c r="AQ10" s="15">
-        <v>6.6546004576310824E-2</v>
+        <v>5.7523739960376706E-2</v>
       </c>
       <c r="AR10" s="15">
-        <v>4.7993212971092845E-2</v>
+        <v>5.4166695518270393E-2</v>
       </c>
       <c r="AS10" s="15">
-        <v>4.5252519773348869E-2</v>
+        <v>4.4354442579946474E-2</v>
       </c>
       <c r="AT10" s="15">
-        <v>4.6622866372220864E-2</v>
+        <v>4.926056904910843E-2</v>
       </c>
       <c r="AU10" s="15">
-        <v>4.1204502576226411E-2</v>
+        <v>3.400421300018782E-2</v>
       </c>
       <c r="AV10" s="15">
-        <v>4.3614820920078026E-2</v>
+        <v>3.4252508815115039E-2</v>
       </c>
       <c r="AW10" s="15">
-        <v>4.2409661748152208E-2</v>
+        <v>3.412836090765143E-2</v>
       </c>
       <c r="AX10" s="15">
-        <v>3.8923052132281609E-2</v>
+        <v>3.2761099566076049E-2</v>
       </c>
       <c r="AY10" s="15">
-        <v>5.3553863939848227E-2</v>
+        <v>3.0881201446874819E-2</v>
       </c>
       <c r="AZ10" s="15">
-        <v>4.6238458036064918E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+        <v>3.1821150506475437E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:52" ht="15.3">
       <c r="A11" s="13"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -2286,7 +2156,7 @@
       <c r="AY11" s="15"/>
       <c r="AZ11" s="15"/>
     </row>
-    <row r="12" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="12" spans="1:52" ht="15.3">
       <c r="A12" s="13"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -2340,9 +2210,9 @@
       <c r="AY12" s="15"/>
       <c r="AZ12" s="15"/>
     </row>
-    <row r="13" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="13" spans="1:52" ht="15.3">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -2380,57 +2250,57 @@
       <c r="AI13" s="15"/>
       <c r="AJ13" s="15"/>
       <c r="AK13" s="15">
-        <v>0.26849519365203339</v>
+        <v>0.24880512131463645</v>
       </c>
       <c r="AL13" s="15">
-        <v>0.34659913846463342</v>
+        <v>0.24393729599413669</v>
       </c>
       <c r="AM13" s="15">
-        <v>0.22806329290189545</v>
+        <v>0.26442697480994215</v>
       </c>
       <c r="AN13" s="15">
-        <v>0.28733121568326442</v>
+        <v>0.25418213540203943</v>
       </c>
       <c r="AO13" s="15">
-        <v>0.30559536781284657</v>
+        <v>0.24701225103767085</v>
       </c>
       <c r="AP13" s="15">
-        <v>0.24981998205640421</v>
+        <v>0.23773139874267235</v>
       </c>
       <c r="AQ13" s="15">
-        <v>0.27770767493462539</v>
+        <v>0.24237182489017162</v>
       </c>
       <c r="AR13" s="15">
-        <v>0.10068970512346855</v>
+        <v>0.24901660011944227</v>
       </c>
       <c r="AS13" s="15">
-        <v>8.1983015152663943E-2</v>
+        <v>0.22938479146543636</v>
       </c>
       <c r="AT13" s="15">
-        <v>0.26399096167166619</v>
+        <v>0.2392006957924393</v>
       </c>
       <c r="AU13" s="15">
-        <v>9.5806708468755788E-2</v>
+        <v>0.24337039516919851</v>
       </c>
       <c r="AV13" s="15">
-        <v>8.7007920333264793E-2</v>
+        <v>0.21382655451862795</v>
       </c>
       <c r="AW13" s="15">
-        <v>0.26179572104427185</v>
+        <v>0.22859847484391321</v>
       </c>
       <c r="AX13" s="15">
-        <v>9.3361461533231785E-2</v>
+        <v>0.23334584387679011</v>
       </c>
       <c r="AY13" s="15">
-        <v>8.6420688737840298E-2</v>
+        <v>0.2255027924007767</v>
       </c>
       <c r="AZ13" s="15">
-        <v>0.2627656365465148</v>
-      </c>
-    </row>
-    <row r="14" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+        <v>0.22942431813878342</v>
+      </c>
+    </row>
+    <row r="14" spans="1:52" ht="15.3">
       <c r="A14" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -2468,55 +2338,55 @@
       <c r="AI14" s="15"/>
       <c r="AJ14" s="15"/>
       <c r="AK14" s="15">
-        <v>-8.5835494633176551E-2</v>
+        <v>-8.3344978076517584E-2</v>
       </c>
       <c r="AL14" s="15">
-        <v>-0.16457733439622149</v>
+        <v>0</v>
       </c>
       <c r="AM14" s="15">
-        <v>-3.4634666510260363E-2</v>
+        <v>-8.6137657761943806E-2</v>
       </c>
       <c r="AN14" s="15">
-        <v>-9.9606000453240931E-2</v>
+        <v>-4.3068828880971903E-2</v>
       </c>
       <c r="AO14" s="15">
-        <v>-0.11428521037393302</v>
+        <v>-7.6397445171751385E-2</v>
       </c>
       <c r="AP14" s="15">
-        <v>-4.6347120886351449E-2</v>
+        <v>-5.7006080976511712E-2</v>
       </c>
       <c r="AQ14" s="15">
-        <v>-8.0316165630142225E-2</v>
+        <v>-6.6701763074131545E-2</v>
       </c>
       <c r="AR14" s="15">
-        <v>-8.7811086312425041E-2</v>
+        <v>-7.4976529186391458E-2</v>
       </c>
       <c r="AS14" s="15">
-        <v>-3.4941792018702664E-2</v>
+        <v>-4.4523113539589459E-2</v>
       </c>
       <c r="AT14" s="15">
-        <v>-6.1376439165563845E-2</v>
+        <v>-5.9749821362990459E-2</v>
       </c>
       <c r="AU14" s="15">
-        <v>-7.7781240023852449E-2</v>
+        <v>-6.6992715204740774E-2</v>
       </c>
       <c r="AV14" s="15">
-        <v>-3.6269954070865654E-2</v>
+        <v>-2.6508631584148182E-2</v>
       </c>
       <c r="AW14" s="15">
-        <v>-5.7025597047359065E-2</v>
+        <v>-4.6750673394444477E-2</v>
       </c>
       <c r="AX14" s="15">
-        <v>-6.8838841852160104E-2</v>
+        <v>-5.5143823009935471E-2</v>
       </c>
       <c r="AY14" s="15">
-        <v>-4.346487766586761E-2</v>
+        <v>-3.6278317466395746E-2</v>
       </c>
       <c r="AZ14" s="15">
-        <v>-5.6151859759013864E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+        <v>-4.5711070238165626E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:52" ht="15.3">
       <c r="A15" s="13"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -2570,9 +2440,9 @@
       <c r="AY15" s="12"/>
       <c r="AZ15" s="12"/>
     </row>
-    <row r="16" spans="1:52" ht="13.5" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="16" spans="1:52" ht="13.5" hidden="1" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="16"/>
@@ -2626,9 +2496,9 @@
       <c r="AY16" s="22"/>
       <c r="AZ16" s="22"/>
     </row>
-    <row r="17" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="17" spans="1:52" ht="15.3" hidden="1">
       <c r="A17" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="23">
         <v>408.96122529907126</v>
@@ -2784,9 +2654,9 @@
         <v>7539.082760930628</v>
       </c>
     </row>
-    <row r="18" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="18" spans="1:52" ht="15.3" hidden="1">
       <c r="A18" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="23">
         <v>647.78110126558602</v>
@@ -2942,9 +2812,9 @@
         <v>8271.8277447682412</v>
       </c>
     </row>
-    <row r="19" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="19" spans="1:52" ht="15.3" hidden="1">
       <c r="A19" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="23">
         <v>58.561791359932037</v>
@@ -3100,9 +2970,9 @@
         <v>1255.8638445821318</v>
       </c>
     </row>
-    <row r="20" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="20" spans="1:52" ht="15.3" hidden="1">
       <c r="A20" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
@@ -3210,9 +3080,9 @@
         <v>65.783991693740418</v>
       </c>
     </row>
-    <row r="21" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="21" spans="1:52" ht="15.3" hidden="1">
       <c r="A21" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
@@ -3320,9 +3190,9 @@
         <v>36.892497357740417</v>
       </c>
     </row>
-    <row r="22" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="22" spans="1:52" ht="15.3" hidden="1">
       <c r="A22" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="23">
         <v>706.34289262551806</v>
@@ -3478,9 +3348,9 @@
         <v>9527.6915893503738</v>
       </c>
     </row>
-    <row r="23" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="23" spans="1:52" ht="15.3" hidden="1">
       <c r="A23" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="23">
         <v>-297.38166732644675</v>
@@ -3636,165 +3506,165 @@
         <v>-1988.6088284197472</v>
       </c>
     </row>
-    <row r="24" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="24" spans="1:52" ht="15.3" hidden="1">
       <c r="A24" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="27" t="s">
-        <v>39</v>
-      </c>
       <c r="C24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AF24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AH24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AI24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AJ24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AK24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AL24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AM24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AN24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AO24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AP24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AQ24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AR24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AS24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AU24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AV24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AW24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AX24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AY24" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AZ24" s="27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:52" ht="15.3" hidden="1">
       <c r="A25" s="28"/>
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
@@ -3862,7 +3732,7 @@
       <c r="AY25" s="31"/>
       <c r="AZ25" s="31"/>
     </row>
-    <row r="26" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="26" spans="1:52" ht="15.3" hidden="1">
       <c r="A26" s="13"/>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
@@ -3962,9 +3832,9 @@
       <c r="AY26" s="25"/>
       <c r="AZ26" s="25"/>
     </row>
-    <row r="27" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="27" spans="1:52" ht="15.3" hidden="1">
       <c r="A27" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="23">
         <v>2590</v>
@@ -4120,9 +3990,9 @@
         <v>39154.682745506419</v>
       </c>
     </row>
-    <row r="28" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="28" spans="1:52" ht="15.3" hidden="1">
       <c r="A28" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="37">
         <v>0.15790008698805841</v>
@@ -4278,9 +4148,9 @@
         <v>0.19254613324113448</v>
       </c>
     </row>
-    <row r="29" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="29" spans="1:52" ht="15.3" hidden="1">
       <c r="A29" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="37">
         <v>0.25010853330717608</v>
@@ -4436,9 +4306,9 @@
         <v>0.21126024180894573</v>
       </c>
     </row>
-    <row r="30" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="30" spans="1:52" ht="15.3" hidden="1">
       <c r="A30" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="37">
         <v>2.2610730254800013E-2</v>
@@ -4594,9 +4464,9 @@
         <v>3.2074422687699104E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="31" spans="1:52" ht="15.3" hidden="1">
       <c r="A31" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B31" s="37"/>
       <c r="C31" s="37"/>
@@ -4704,9 +4574,9 @@
         <v>1.6801053432437812E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="32" spans="1:52" ht="15.3" hidden="1">
       <c r="A32" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B32" s="37"/>
       <c r="C32" s="37"/>
@@ -4814,9 +4684,9 @@
         <v>9.4222439746301809E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="33" spans="1:52" ht="15.3" hidden="1">
       <c r="A33" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="37">
         <v>0.27271926356197607</v>
@@ -4972,9 +4842,9 @@
         <v>0.24333466449664484</v>
       </c>
     </row>
-    <row r="34" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="34" spans="1:52" ht="15.3" hidden="1">
       <c r="A34" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="37">
         <v>-0.11481917657391766</v>
@@ -5130,14 +5000,14 @@
         <v>-5.0788531255510416E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:52">
       <c r="A35" s="40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:52" ht="15">
+      <c r="A36" s="41" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:52" ht="16" x14ac:dyDescent="0.8">
-      <c r="A36" s="41" t="s">
-        <v>41</v>
       </c>
       <c r="AI36" s="42" t="str">
         <f>+AI6</f>
@@ -5206,7 +5076,7 @@
         <v>2029/2030</v>
       </c>
     </row>
-    <row r="37" spans="1:52" ht="16" x14ac:dyDescent="0.8">
+    <row r="37" spans="1:52" ht="15.3">
       <c r="A37" s="46" t="str">
         <f>+A34</f>
         <v>Deficit (Excl. Grants ) % of GDP</v>
@@ -5284,7 +5154,7 @@
         <v>-5.0788531255510416E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:52" ht="14.1">
       <c r="A38" s="99" t="str">
         <f>+A51</f>
         <v xml:space="preserve">correction </v>
@@ -5298,7 +5168,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="AN38" s="48">
-        <f t="shared" si="2"/>
+        <f>-AN51</f>
         <v>0</v>
       </c>
       <c r="AO38" s="48">
@@ -5350,9 +5220,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:52" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="39" spans="1:52" ht="14.1" thickBot="1">
       <c r="A39" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AL39" s="50">
         <f>+AL37+AL38</f>
@@ -5415,9 +5285,9 @@
         <v>-5.0788531255510416E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:52" ht="14.4" thickTop="1">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AL40" s="51">
         <f>+AL46-AL53-AL60</f>
@@ -5462,9 +5332,9 @@
         <v>-5.0430582505264485E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:52" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="41" spans="1:52" ht="14.4" thickBot="1">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AL41" s="58">
         <f>+AL47-AL54-AL61</f>
@@ -5527,8 +5397,8 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75"/>
-    <row r="43" spans="1:52" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:52" ht="14.1" thickTop="1"/>
+    <row r="43" spans="1:52" ht="16.5" customHeight="1">
       <c r="A43" s="65" t="str">
         <f>+A28</f>
         <v>Grev in % of GDP</v>
@@ -5606,7 +5476,7 @@
         <v>0.19254613324113448</v>
       </c>
     </row>
-    <row r="44" spans="1:52" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:52" ht="16.5" customHeight="1">
       <c r="A44" s="99" t="str">
         <f>+A51</f>
         <v xml:space="preserve">correction </v>
@@ -5670,9 +5540,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:52" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="45" spans="1:52" ht="16.5" customHeight="1" thickBot="1">
       <c r="A45" s="49" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AI45" s="15"/>
       <c r="AJ45" s="15"/>
@@ -5741,9 +5611,9 @@
         <v>0.19254613324113448</v>
       </c>
     </row>
-    <row r="46" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:52" ht="14.4" thickTop="1">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI46" s="57">
         <f>+AI43-AI48</f>
@@ -5799,9 +5669,9 @@
       </c>
       <c r="AZ46" s="15"/>
     </row>
-    <row r="47" spans="1:52" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="47" spans="1:52" ht="14.4" thickBot="1">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AI47" s="57">
         <f>+AI43+AI48</f>
@@ -5876,7 +5746,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:52" ht="14.1" thickTop="1">
       <c r="AI48" s="66">
         <v>2E-3</v>
       </c>
@@ -5938,7 +5808,7 @@
         <v>0.19315000000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:55" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:55">
       <c r="AI49" s="66"/>
       <c r="AJ49" s="66"/>
       <c r="AK49" s="66"/>
@@ -5958,7 +5828,7 @@
       <c r="AY49" s="66"/>
       <c r="AZ49" s="66"/>
     </row>
-    <row r="50" spans="1:55" ht="15.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:55" ht="15.55" customHeight="1">
       <c r="A50" s="65" t="str">
         <f>+A29</f>
         <v>Gdem in % of GDP</v>
@@ -6036,9 +5906,9 @@
         <v>0.21126024180894573</v>
       </c>
     </row>
-    <row r="51" spans="1:55" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:55">
       <c r="A51" s="67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AI51" s="68">
         <v>0</v>
@@ -6107,9 +5977,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="52" spans="1:55" ht="14.4" thickBot="1">
       <c r="A52" s="49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AI52" s="69">
         <f t="shared" ref="AI52:AZ52" si="11">+AI50+AI51</f>
@@ -6184,9 +6054,9 @@
         <v>0.21126024180894573</v>
       </c>
     </row>
-    <row r="53" spans="1:55" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:55" ht="14.4" thickTop="1">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AI53" s="15"/>
       <c r="AJ53" s="57"/>
@@ -6237,7 +6107,7 @@
       </c>
       <c r="AZ53" s="57"/>
     </row>
-    <row r="54" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="54" spans="1:55" ht="14.4" thickBot="1">
       <c r="A54" t="str">
         <f>+A47</f>
         <v xml:space="preserve">                                                 second Q in sem</v>
@@ -6306,7 +6176,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:55" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:55" ht="14.1" thickTop="1">
       <c r="AI55" s="15"/>
       <c r="AJ55" s="15"/>
       <c r="AK55" s="15"/>
@@ -6326,7 +6196,7 @@
       <c r="AY55" s="15"/>
       <c r="AZ55" s="15"/>
     </row>
-    <row r="56" spans="1:55" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:55">
       <c r="A56" s="65" t="str">
         <f>+A30</f>
         <v>Other Expenditure of %GDP</v>
@@ -6404,9 +6274,9 @@
         <v>3.2074422687699104E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:55" s="70" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:55" s="70" customFormat="1">
       <c r="A57" s="70" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF57" s="71"/>
       <c r="AG57" s="71"/>
@@ -6481,7 +6351,7 @@
         <v>9.4222439746301809E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:55" s="67" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:55" s="67" customFormat="1">
       <c r="A58" s="67" t="str">
         <f>+A38</f>
         <v xml:space="preserve">correction </v>
@@ -6557,9 +6427,9 @@
       <c r="BB58" s="68"/>
       <c r="BC58" s="68"/>
     </row>
-    <row r="59" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="59" spans="1:55" ht="14.1" thickBot="1">
       <c r="A59" s="49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AI59" s="50">
         <f t="shared" ref="AI59:AK59" si="15">+AI56+AI58</f>
@@ -6637,9 +6507,9 @@
       <c r="BB59" s="50"/>
       <c r="BC59" s="50"/>
     </row>
-    <row r="60" spans="1:55" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:55" ht="14.4" thickTop="1">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL60" s="51">
         <f>+AL59</f>
@@ -6687,7 +6557,7 @@
       </c>
       <c r="AZ60" s="57"/>
     </row>
-    <row r="61" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="61" spans="1:55" ht="14.4" thickBot="1">
       <c r="A61" t="str">
         <f>+A54</f>
         <v xml:space="preserve">                                                 second Q in sem</v>
@@ -6753,9 +6623,9 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:55" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:55" ht="14.1" thickTop="1">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AN62" s="47">
         <f>+AN59-AN57</f>
@@ -6778,9 +6648,9 @@
         <v>3.1132198290236085E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:55" ht="13.5" customHeight="1">
       <c r="A64" s="76" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI64" s="77" t="str">
         <f t="shared" ref="AI64:AK64" si="19">+IF(ABS(AI43-AI50-AI56-AI37)&gt;0.1,"check","")</f>
@@ -6855,7 +6725,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:53" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:53">
       <c r="A65" s="76" t="str">
         <f>+A64</f>
         <v>check</v>
@@ -6932,24 +6802,21 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="BA65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:53" x14ac:dyDescent="0.75">
+    </row>
+    <row r="66" spans="1:53">
       <c r="AI66" s="94" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ66" s="95" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:53" x14ac:dyDescent="0.75">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:53">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AI67" s="96" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ67" s="97">
         <v>840.56</v>
@@ -7017,14 +6884,11 @@
         <f t="shared" si="23"/>
         <v>36.892497357740417</v>
       </c>
-      <c r="BA67" s="93">
-        <f>+AK67+AN67+AQ67+AT67+AW67+AZ67</f>
-        <v>1508.1120582726448</v>
-      </c>
-    </row>
-    <row r="68" spans="1:53" x14ac:dyDescent="0.75">
+      <c r="BA67" s="93"/>
+    </row>
+    <row r="68" spans="1:53">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AI68" s="79"/>
       <c r="AJ68" s="98">
@@ -7047,9 +6911,9 @@
       <c r="AY68" s="82"/>
       <c r="AZ68" s="82"/>
     </row>
-    <row r="69" spans="1:53" s="70" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:53" s="70" customFormat="1">
       <c r="A69" s="70" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF69" s="71"/>
       <c r="AG69" s="71"/>
@@ -7121,7 +6985,7 @@
         <v>9.4222439746301809E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:53" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:53">
       <c r="AL71" s="44" t="str">
         <f>+AL36</f>
         <v>Jul-Dec</v>
@@ -7148,14 +7012,14 @@
       </c>
       <c r="AR71" s="44"/>
     </row>
-    <row r="72" spans="1:53" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:53">
       <c r="AJ72" s="92" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="73" spans="1:53" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:53" ht="14.1" thickBot="1">
       <c r="A73" s="65" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AJ73" s="84">
         <f>+AVERAGE(AN73,AQ73)</f>
@@ -7203,12 +7067,12 @@
       <c r="AY73" s="47"/>
       <c r="AZ73" s="47"/>
     </row>
-    <row r="74" spans="1:53" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:53" ht="14.1" thickTop="1">
       <c r="A74" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ74" s="45" t="s">
         <v>54</v>
-      </c>
-      <c r="AJ74" s="45" t="s">
-        <v>55</v>
       </c>
       <c r="AL74" s="85">
         <f>+$AJ$73/$AJ$75*$AJ$78*AL77</f>
@@ -7238,9 +7102,9 @@
       </c>
       <c r="AT74" s="55"/>
     </row>
-    <row r="75" spans="1:53" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="75" spans="1:53" ht="14.1" thickBot="1">
       <c r="A75" s="70" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AJ75" s="89">
         <v>0.15</v>
@@ -7282,17 +7146,17 @@
         <v>4.124610152328733E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:53" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:53" ht="14.1" thickTop="1">
       <c r="A76" s="70"/>
       <c r="AJ76" s="89"/>
       <c r="AN76" s="105"/>
     </row>
-    <row r="77" spans="1:53" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:53">
       <c r="AJ77" s="45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AK77" s="45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AL77" s="90">
         <v>0.65</v>
@@ -7315,7 +7179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:53" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:53">
       <c r="AJ78" s="90">
         <v>0.5</v>
       </c>
@@ -7340,9 +7204,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:53" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:53">
       <c r="A79" s="91" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AN79" s="90"/>
     </row>
@@ -7354,214 +7218,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD3143F-1CB5-4284-805F-149289AA16B5}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
-  <cols>
-    <col min="1" max="1" width="53.6796875" customWidth="1"/>
-    <col min="2" max="8" width="8.86328125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD3143F-1CB5-4284-805F-149289AA16B5}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:1">
       <c r="A1" s="1"/>
-      <c r="B1" s="114">
-        <v>2024</v>
-      </c>
-      <c r="C1" s="114">
-        <v>2025</v>
-      </c>
-      <c r="D1" s="114">
-        <v>2026</v>
-      </c>
-      <c r="E1" s="114">
-        <v>2027</v>
-      </c>
-      <c r="F1" s="114">
-        <v>2028</v>
-      </c>
-      <c r="G1" s="114">
-        <v>2029</v>
-      </c>
-      <c r="H1" s="114">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A2" s="106" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="110">
-        <f>C3+C4</f>
-        <v>308.85861037162039</v>
-      </c>
-      <c r="D2" s="110">
-        <f t="shared" ref="D2:G2" si="0">D3+D4</f>
-        <v>721.33994120659054</v>
-      </c>
-      <c r="E2" s="110">
-        <f t="shared" si="0"/>
-        <v>732.21927019834698</v>
-      </c>
-      <c r="F2" s="110">
-        <f t="shared" si="0"/>
-        <v>187.93653864476565</v>
-      </c>
-      <c r="G2" s="110">
-        <f t="shared" si="0"/>
-        <v>4.2285111869296426</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A3" s="107" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="110">
-        <v>174.00361037162037</v>
-      </c>
-      <c r="D3" s="110">
-        <v>385.4857976103541</v>
-      </c>
-      <c r="E3" s="110">
-        <v>439.33156211900854</v>
-      </c>
-      <c r="F3" s="110">
-        <v>112.76192318685943</v>
-      </c>
-      <c r="G3" s="110">
-        <v>2.5371067121577857</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A4" s="107" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="111">
-        <v>134.85500000000002</v>
-      </c>
-      <c r="D4" s="111">
-        <v>335.85414359623644</v>
-      </c>
-      <c r="E4" s="111">
-        <v>292.88770807933849</v>
-      </c>
-      <c r="F4" s="111">
-        <v>75.174615457906214</v>
-      </c>
-      <c r="G4" s="111">
-        <v>1.6914044747718571</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="2"/>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A6" s="108" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="109">
-        <v>1382.9873419999999</v>
-      </c>
-      <c r="C6" s="109">
-        <v>1455.0205468858974</v>
-      </c>
-      <c r="D6" s="109">
-        <v>1517.7698205635791</v>
-      </c>
-      <c r="E6" s="109">
-        <v>1572.0012687572651</v>
-      </c>
-      <c r="F6" s="109">
-        <v>1615.7148947336634</v>
-      </c>
-      <c r="G6" s="109">
-        <v>1656.1077671020048</v>
-      </c>
-      <c r="H6" s="109">
-        <v>1697.5104612795549</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="112">
-        <f>C6/B6-1</f>
-        <v>5.2085223557958971E-2</v>
-      </c>
-      <c r="D7" s="112">
-        <f t="shared" ref="D7:H7" si="1">D6/C6-1</f>
-        <v>4.312603956829375E-2</v>
-      </c>
-      <c r="E7" s="112">
-        <f t="shared" si="1"/>
-        <v>3.5731009708408035E-2</v>
-      </c>
-      <c r="F7" s="112">
-        <f t="shared" si="1"/>
-        <v>2.7807627668746004E-2</v>
-      </c>
-      <c r="G7" s="112">
-        <f t="shared" si="1"/>
-        <v>2.4999999999999911E-2</v>
-      </c>
-      <c r="H7" s="112">
-        <f t="shared" si="1"/>
-        <v>2.4999999999999911E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="109">
-        <v>1256.9432939166666</v>
-      </c>
-      <c r="C8" s="109">
-        <v>1370.8647181798078</v>
-      </c>
-      <c r="D8" s="109">
-        <v>1452.6995640838434</v>
-      </c>
-      <c r="E8" s="109">
-        <v>1515.6403641925801</v>
-      </c>
-      <c r="F8" s="109">
-        <v>1569.371813202943</v>
-      </c>
-      <c r="G8" s="109">
-        <v>1614.8847063316493</v>
-      </c>
-      <c r="H8" s="109">
-        <v>1656.360222554307</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="C9" s="112"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="C10" s="113">
-        <f>C2*C6/1000</f>
-        <v>449.39562417333343</v>
-      </c>
-      <c r="D10" s="113">
-        <f t="shared" ref="D10:G10" si="2">D2*D6/1000</f>
-        <v>1094.8279931304696</v>
-      </c>
-      <c r="E10" s="113">
-        <f t="shared" si="2"/>
-        <v>1151.0496217603202</v>
-      </c>
-      <c r="F10" s="113">
-        <f t="shared" si="2"/>
-        <v>303.65186475303659</v>
-      </c>
-      <c r="G10" s="113">
-        <f t="shared" si="2"/>
-        <v>7.0028702199518982</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>